--- a/범운해운항공_전체데이터_통합백업_2026-10-31.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-31.xlsx
@@ -14279,7 +14279,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>의약품</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>의약품</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr"/>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>의약품</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -14600,7 +14600,7 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr"/>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>의약품</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr"/>
@@ -14819,7 +14819,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>의약품/화장품</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr"/>
@@ -14909,7 +14909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15161,7 +15161,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -15176,17 +15176,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>의약품</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>35000</v>
+        <v>77340</v>
       </c>
       <c r="G8" t="n">
-        <v>25000</v>
+        <v>37340</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15195,7 +15195,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>주식회사 케이티글로발</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -15210,17 +15210,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>보톡스 필러</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15229,7 +15229,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>주식회사 케이티글로발</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -15244,17 +15244,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>41340</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>41340</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>필러</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -15297,32 +15297,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>텐트러스트</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>특가품목</t>
+          <t>필러</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>30000</v>
+        <v>41340</v>
       </c>
       <c r="G12" t="n">
-        <v>30000</v>
+        <v>41340</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -15336,12 +15336,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>항공(Air)</t>
+          <t>해상(LCL)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15353,10 +15353,10 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>30840</v>
+        <v>30000</v>
       </c>
       <c r="G13" t="n">
-        <v>30840</v>
+        <v>30000</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -15365,32 +15365,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>맥익스프레스 인터내셔날(주)</t>
+          <t>텐트러스트</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>특가품목</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>42000</v>
+        <v>30840</v>
       </c>
       <c r="G14" t="n">
-        <v>42000</v>
+        <v>30840</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -15414,17 +15414,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>필러</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>45000</v>
+        <v>42000</v>
       </c>
       <c r="G15" t="n">
-        <v>45000</v>
+        <v>42000</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -15433,41 +15433,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>리턴의원</t>
+          <t>맥익스프레스 인터내셔날(주)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>항공(Air)</t>
+          <t>해상(LCL)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>보톡스 필러 (Botox &amp; Filler)</t>
+          <t>필러</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>38000</v>
+        <v>45000</v>
       </c>
       <c r="G16" t="n">
-        <v>25000</v>
+        <v>45000</v>
       </c>
       <c r="H16" t="n">
-        <v>3700000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>뷰메디스</t>
+          <t>리턴의원</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -15482,20 +15482,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>보톡스 필러 (Botox &amp; Filler)</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>39840</v>
+        <v>38000</v>
       </c>
       <c r="G17" t="n">
-        <v>39840</v>
+        <v>25000</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="18">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>필러</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -15535,34 +15535,68 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>유에스퀵</t>
+          <t>뷰메디스</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>필러</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
+        <v>39840</v>
+      </c>
+      <c r="G19" t="n">
+        <v>39840</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>유에스퀵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>해상(LCL)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
         <v>8500</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>8500</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15590,7 +15624,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 24340, "추가단가": 24340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": ""}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "", "담당자": "히엔/이동렬", "전화번호": "", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "주식회사 케이티글로발": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "", "담당자": "박수진", "전화번호": "", "주소": ""}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "리턴의원": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "뷰메디스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "유에스퀵": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 37000, "추가단가": 27000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 37000, "추가단가": 27000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리", "지급상태": "미지급"}, {"날짜": "2026-10-30", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 120000, "적요": "양공열 식사 90000만원 대리비용30000원", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 24340, "추가단가": 24340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}, "의약품": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": ""}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "", "담당자": "히엔/이동렬", "전화번호": "", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "주식회사 케이티글로발": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "", "담당자": "박수진", "전화번호": "", "주소": ""}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "리턴의원": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "뷰메디스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "유에스퀵": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 37000, "추가단가": 27000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 37000, "추가단가": 27000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리", "지급상태": "미지급"}, {"날짜": "2026-10-30", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 120000, "적요": "양공열 식사 90000만원 대리비용30000원", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-31.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-31.xlsx
@@ -15624,7 +15624,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 24340, "추가단가": 24340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}, "의약품": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": ""}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "", "담당자": "히엔/이동렬", "전화번호": "", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "주식회사 케이티글로발": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "", "담당자": "박수진", "전화번호": "", "주소": ""}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "리턴의원": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "뷰메디스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "유에스퀵": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 37000, "추가단가": 27000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 37000, "추가단가": 27000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리", "지급상태": "미지급"}, {"날짜": "2026-10-30", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 120000, "적요": "양공열 식사 90000만원 대리비용30000원", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 24340, "추가단가": 24340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}, "의약품": {"기본중량": 1.0, "기본요금": 77340, "추가단가": 37340, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 41340, "추가단가": 41340, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": ""}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "", "담당자": "히엔/이동렬", "전화번호": "", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "주식회사 케이티글로발": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "", "담당자": "박수진", "전화번호": "", "주소": ""}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "리턴의원": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "뷰메디스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "유에스퀵": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 37000, "추가단가": 27000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 37000, "추가단가": 27000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "지급완료"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "지급완료"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "지급완료"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "지급완료"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "지급완료"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "지급완료"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "지급완료"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리", "지급상태": "지급완료"}, {"날짜": "2026-10-30", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 120000, "적요": "양공열 식사 90000만원 대리비용30000원", "지급상태": "지급완료"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록 후 수정 승인 대기", "연결 B/L 번호": "BW260027", "변경요청JSON": "{\"요청일시\": \"2026-10-31 03:40:01\", \"요청자\": \"주식회사 조은로직스\", \"변경후\": {\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"B/L 등록 후 수정 승인 대기\", \"연결 B/L 번호\": \"BW260027\", \"변경요청JSON\": \"{\\\"요청일시\\\": \\\"2026-10-31 03:39:59\\\", \\\"요청자\\\": \\\"주식회사 조은로직스\\\", \\\"변경후\\\": {\\\"접수번호\\\": \\\"REQ-A458BDB2B3\\\", \\\"접수일시\\\": \\\"2026-10-24 03:53:51\\\", \\\"고객사아이디\\\": \\\"joeun\\\", \\\"고객사상호\\\": \\\"주식회사 조은로직스\\\", \\\"화주상호\\\": \\\"주식회사 조은로직스\\\", \\\"화주주소\\\": \\\"112\\\", \\\"화주전화번호\\\": \\\"2112\\\", \\\"해외수하인\\\": \\\"1212\\\", \\\"해외수하인주소\\\": \\\"121\\\", \\\"해외수하인전화번호\\\": \\\"121\\\", \\\"도착국가\\\": \\\"미국\\\", \\\"품목\\\": \\\"보톡스\\\", \\\"운송형태\\\": \\\"항공(Air)\\\", \\\"실제중량kg\\\": \\\"10.00\\\", \\\"가로cm\\\": \\\"25.50\\\", \\\"세로cm\\\": \\\"35.00\\\", \\\"높이cm\\\": \\\"10.00\\\", \\\"박스수량\\\": \\\"1\\\", \\\"CBM\\\": \\\"0.0089\\\", \\\"부피중량kg\\\": \\\"1.78\\\", \\\"추가요청\\\": \\\"\\\", \\\"상태\\\": \\\"B/L 등록\\\", \\\"연결 B/L 번호\\\": \\\"BW260027\\\", \\\"변경요청JSON\\\": \\\"\\\", \\\"관리자메모\\\": \\\"\\\", \\\"승인일시\\\": \\\"2026-10-24 04:13:29\\\", \\\"승인자\\\": \\\"lsb\\\", \\\"B/L등록일시\\\": \\\"2026-10-24 04:28:57\\\", \\\"박스별정보JSON\\\": \\\"\\\", \\\"바코드목록JSON\\\": \\\"\\\", \\\"수출면장번호\\\": \\\"\\\"}}\", \"관리자메모\": \"\", \"승인일시\": \"2026-10-24 04:13:29\", \"승인자\": \"lsb\", \"B/L등록일시\": \"2026-10-24 04:28:57\", \"박스별정보JSON\": \"\", \"바코드목록JSON\": \"\", \"수출면장번호\": \"\"}}", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57", "박스별정보JSON": "[{\"박스순번\": 1, \"가로cm\": 25.5, \"세로cm\": 35.0, \"높이cm\": 10.0, \"바코드\": \"BW261031-6910F6F3\", \"입고상태\": \"미입고\"}]", "바코드목록JSON": "[\"BW261031-6910F6F3\"]", "수출면장번호": ""}, {"접수번호": "REQ-1352AC8EF3", "접수일시": "2026-10-31 03:34:11", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "we", "화주전화번호": "ewwe", "해외수하인": "wew", "해외수하인주소": "wew", "해외수하인전화번호": "we", "도착국가": "미국", "품목": "일반화물", "운송형태": "항공(Air)", "실제중량kg": "2.00", "가로cm": "26.00", "세로cm": "33.00", "높이cm": "45.00", "박스수량": "1", "CBM": "0.0386", "부피중량kg": "7.72", "추가요청": "", "상태": "접수", "연결 B/L 번호": "", "변경요청JSON": "", "관리자메모": "", "승인일시": "", "승인자": "", "B/L등록일시": "", "박스별정보JSON": "[{\"박스순번\": 1, \"가로cm\": 26.0, \"세로cm\": 33.0, \"높이cm\": 45.0, \"실제중량kg\": \"\", \"바코드\": \"BW261031-30199F3C\", \"입고상태\": \"미입고\"}]", "바코드목록JSON": "[\"BW261031-30199F3C\"]", "수출면장번호": ""}, {"접수번호": "REQ-8D0365C209", "접수일시": "2026-10-31 03:34:11", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "we", "화주전화번호": "ewwe", "해외수하인": "wew", "해외수하인주소": "wew", "해외수하인전화번호": "we", "도착국가": "미국", "품목": "일반화물", "운송형태": "항공(Air)", "실제중량kg": "2.00", "가로cm": "26.00", "세로cm": "33.00", "높이cm": "45.00", "박스수량": "1", "CBM": "0.0386", "부피중량kg": "7.72", "추가요청": "", "상태": "접수", "연결 B/L 번호": "", "변경요청JSON": "", "관리자메모": "", "승인일시": "", "승인자": "", "B/L등록일시": "", "박스별정보JSON": "[{\"박스순번\": 1, \"가로cm\": 26.0, \"세로cm\": 33.0, \"높이cm\": 45.0, \"실제중량kg\": \"\", \"바코드\": \"BW261031-5EAD2C54\", \"입고상태\": \"미입고\"}]", "바코드목록JSON": "[\"BW261031-5EAD2C54\"]", "수출면장번호": ""}, {"접수번호": "REQ-F3132C22A5", "접수일시": "2026-10-31 03:34:29", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "we", "화주전화번호": "ewwe", "해외수하인": "wew", "해외수하인주소": "wew", "해외수하인전화번호": "we", "도착국가": "미국", "품목": "일반화물", "운송형태": "항공(Air)", "실제중량kg": "2.00", "가로cm": "26.00", "세로cm": "33.00", "높이cm": "45.00", "박스수량": "1", "CBM": "0.0386", "부피중량kg": "7.72", "추가요청": "", "상태": "접수", "연결 B/L 번호": "", "변경요청JSON": "", "관리자메모": "", "승인일시": "", "승인자": "", "B/L등록일시": "", "박스별정보JSON": "[{\"박스순번\": 1, \"가로cm\": 26.0, \"세로cm\": 33.0, \"높이cm\": 45.0, \"실제중량kg\": \"\", \"바코드\": \"BW261031-EE30092E\", \"입고상태\": \"미입고\"}]", "바코드목록JSON": "[\"BW261031-EE30092E\"]", "수출면장번호": ""}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}, {"일시": "2026-10-31 03:34:00", "접수번호": "REQ-5E48AE99B9", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수 및 박스별 바코드 발급", "변경내용": "{\"접수번호\": \"REQ-5E48AE99B9\", \"접수일시\": \"2026-10-31 03:34:00\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"we\", \"화주전화번호\": \"ewwe\", \"해외수하인\": \"wew\", \"해외수하인주소\": \"wew\", \"해외수하인전화번호\": \"we\", \"도착국가\": \"미국\", \"품목\": \"일반화물\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"2.00\", \"가로cm\": \"26.00\", \"세로cm\": \"33.00\", \"높이cm\": \"45.00\", \"박스수량\": \"1\", \"CBM\": \"0.0386\", \"부피중량kg\": \"7.72\", \"박스별정보JSON\": \"[{\\\"박스순번\\\": 1, \\\"가로cm\\\": 26.0, \\\"세로cm\\\": 33.0, \\\"높이cm\\\": 45.0, \\\"실제중량kg\\\": \\\"\\\", \\\"바코드\\\": \\\"BW261031-AF70AD8A\\\", \\\"입고상태\\\": \\\"미입고\\\"}]\", \"바코드목록JSON\": \"[\\\"BW261031-AF70AD8A\\\"]\", \"수출면장번호\": \"\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-31 03:34:11", "접수번호": "REQ-1352AC8EF3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수 및 박스별 바코드 발급", "변경내용": "{\"접수번호\": \"REQ-1352AC8EF3\", \"접수일시\": \"2026-10-31 03:34:11\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"we\", \"화주전화번호\": \"ewwe\", \"해외수하인\": \"wew\", \"해외수하인주소\": \"wew\", \"해외수하인전화번호\": \"we\", \"도착국가\": \"미국\", \"품목\": \"일반화물\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"2.00\", \"가로cm\": \"26.00\", \"세로cm\": \"33.00\", \"높이cm\": \"45.00\", \"박스수량\": \"1\", \"CBM\": \"0.0386\", \"부피중량kg\": \"7.72\", \"박스별정보JSON\": \"[{\\\"박스순번\\\": 1, \\\"가로cm\\\": 26.0, \\\"세로cm\\\": 33.0, \\\"높이cm\\\": 45.0, \\\"실제중량kg\\\": \\\"\\\", \\\"바코드\\\": \\\"BW261031-30199F3C\\\", \\\"입고상태\\\": \\\"미입고\\\"}]\", \"바코드목록JSON\": \"[\\\"BW261031-30199F3C\\\"]\", \"수출면장번호\": \"\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-31 03:34:11", "접수번호": "REQ-8D0365C209", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수 및 박스별 바코드 발급", "변경내용": "{\"접수번호\": \"REQ-8D0365C209\", \"접수일시\": \"2026-10-31 03:34:11\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"we\", \"화주전화번호\": \"ewwe\", \"해외수하인\": \"wew\", \"해외수하인주소\": \"wew\", \"해외수하인전화번호\": \"we\", \"도착국가\": \"미국\", \"품목\": \"일반화물\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"2.00\", \"가로cm\": \"26.00\", \"세로cm\": \"33.00\", \"높이cm\": \"45.00\", \"박스수량\": \"1\", \"CBM\": \"0.0386\", \"부피중량kg\": \"7.72\", \"박스별정보JSON\": \"[{\\\"박스순번\\\": 1, \\\"가로cm\\\": 26.0, \\\"세로cm\\\": 33.0, \\\"높이cm\\\": 45.0, \\\"실제중량kg\\\": \\\"\\\", \\\"바코드\\\": \\\"BW261031-5EAD2C54\\\", \\\"입고상태\\\": \\\"미입고\\\"}]\", \"바코드목록JSON\": \"[\\\"BW261031-5EAD2C54\\\"]\", \"수출면장번호\": \"\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-31 03:34:29", "접수번호": "REQ-F3132C22A5", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수 및 박스별 바코드 발급", "변경내용": "{\"접수번호\": \"REQ-F3132C22A5\", \"접수일시\": \"2026-10-31 03:34:29\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"we\", \"화주전화번호\": \"ewwe\", \"해외수하인\": \"wew\", \"해외수하인주소\": \"wew\", \"해외수하인전화번호\": \"we\", \"도착국가\": \"미국\", \"품목\": \"일반화물\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"2.00\", \"가로cm\": \"26.00\", \"세로cm\": \"33.00\", \"높이cm\": \"45.00\", \"박스수량\": \"1\", \"CBM\": \"0.0386\", \"부피중량kg\": \"7.72\", \"박스별정보JSON\": \"[{\\\"박스순번\\\": 1, \\\"가로cm\\\": 26.0, \\\"세로cm\\\": 33.0, \\\"높이cm\\\": 45.0, \\\"실제중량kg\\\": \\\"\\\", \\\"바코드\\\": \\\"BW261031-EE30092E\\\", \\\"입고상태\\\": \\\"미입고\\\"}]\", \"바코드목록JSON\": \"[\\\"BW261031-EE30092E\\\"]\", \"수출면장번호\": \"\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-31 03:39:59", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 후 수정 승인 요청", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"B/L 등록\", \"연결 B/L 번호\": \"BW260027\", \"변경요청JSON\": \"\", \"관리자메모\": \"\", \"승인일시\": \"2026-10-24 04:13:29\", \"승인자\": \"lsb\", \"B/L등록일시\": \"2026-10-24 04:28:57\", \"박스별정보JSON\": \"\", \"바코드목록JSON\": \"\", \"수출면장번호\": \"\"}"}, {"일시": "2026-10-31 03:40:01", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 후 수정 승인 요청", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"B/L 등록 후 수정 승인 대기\", \"연결 B/L 번호\": \"BW260027\", \"변경요청JSON\": \"{\\\"요청일시\\\": \\\"2026-10-31 03:39:59\\\", \\\"요청자\\\": \\\"주식회사 조은로직스\\\", \\\"변경후\\\": {\\\"접수번호\\\": \\\"REQ-A458BDB2B3\\\", \\\"접수일시\\\": \\\"2026-10-24 03:53:51\\\", \\\"고객사아이디\\\": \\\"joeun\\\", \\\"고객사상호\\\": \\\"주식회사 조은로직스\\\", \\\"화주상호\\\": \\\"주식회사 조은로직스\\\", \\\"화주주소\\\": \\\"112\\\", \\\"화주전화번호\\\": \\\"2112\\\", \\\"해외수하인\\\": \\\"1212\\\", \\\"해외수하인주소\\\": \\\"121\\\", \\\"해외수하인전화번호\\\": \\\"121\\\", \\\"도착국가\\\": \\\"미국\\\", \\\"품목\\\": \\\"보톡스\\\", \\\"운송형태\\\": \\\"항공(Air)\\\", \\\"실제중량kg\\\": \\\"10.00\\\", \\\"가로cm\\\": \\\"25.50\\\", \\\"세로cm\\\": \\\"35.00\\\", \\\"높이cm\\\": \\\"10.00\\\", \\\"박스수량\\\": \\\"1\\\", \\\"CBM\\\": \\\"0.0089\\\", \\\"부피중량kg\\\": \\\"1.78\\\", \\\"추가요청\\\": \\\"\\\", \\\"상태\\\": \\\"B/L 등록\\\", \\\"연결 B/L 번호\\\": \\\"BW260027\\\", \\\"변경요청JSON\\\": \\\"\\\", \\\"관리자메모\\\": \\\"\\\", \\\"승인일시\\\": \\\"2026-10-24 04:13:29\\\", \\\"승인자\\\": \\\"lsb\\\", \\\"B/L등록일시\\\": \\\"2026-10-24 04:28:57\\\", \\\"박스별정보JSON\\\": \\\"\\\", \\\"바코드목록JSON\\\": \\\"\\\", \\\"수출면장번호\\\": \\\"\\\"}}\", \"관리자메모\": \"\", \"승인일시\": \"2026-10-24 04:13:29\", \"승인자\": \"lsb\", \"B/L등록일시\": \"2026-10-24 04:28:57\", \"박스별정보JSON\": \"\", \"바코드목록JSON\": \"\", \"수출면장번호\": \"\"}"}, {"일시": "2026-10-31 03:45:21", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "기존 접수 건 QR·바코드 보완 발급", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"B/L 등록 후 수정 승인 대기\", \"연결 B/L 번호\": \"BW260027\", \"변경요청JSON\": \"{\\\"요청일시\\\": \\\"2026-10-31 03:40:01\\\", \\\"요청자\\\": \\\"주식회사 조은로직스\\\", \\\"변경후\\\": {\\\"접수번호\\\": \\\"REQ-A458BDB2B3\\\", \\\"접수일시\\\": \\\"2026-10-24 03:53:51\\\", \\\"고객사아이디\\\": \\\"joeun\\\", \\\"고객사상호\\\": \\\"주식회사 조은로직스\\\", \\\"화주상호\\\": \\\"주식회사 조은로직스\\\", \\\"화주주소\\\": \\\"112\\\", \\\"화주전화번호\\\": \\\"2112\\\", \\\"해외수하인\\\": \\\"1212\\\", \\\"해외수하인주소\\\": \\\"121\\\", \\\"해외수하인전화번호\\\": \\\"121\\\", \\\"도착국가\\\": \\\"미국\\\", \\\"품목\\\": \\\"보톡스\\\", \\\"운송형태\\\": \\\"항공(Air)\\\", \\\"실제중량kg\\\": \\\"10.00\\\", \\\"가로cm\\\": \\\"25.50\\\", \\\"세로cm\\\": \\\"35.00\\\", \\\"높이cm\\\": \\\"10.00\\\", \\\"박스수량\\\": \\\"1\\\", \\\"CBM\\\": \\\"0.0089\\\", \\\"부피중량kg\\\": \\\"1.78\\\", \\\"추가요청\\\": \\\"\\\", \\\"상태\\\": \\\"B/L 등록 후 수정 승인 대기\\\", \\\"연결 B/L 번호\\\": \\\"BW260027\\\", \\\"변경요청JSON\\\": \\\"{\\\\\\\"요청일시\\\\\\\": \\\\\\\"2026-10-31 03:39:59\\\\\\\", \\\\\\\"요청자\\\\\\\": \\\\\\\"주식회사 조은로직스\\\\\\\", \\\\\\\"변경후\\\\\\\": {\\\\\\\"접수번호\\\\\\\": \\\\\\\"REQ-A458BDB2B3\\\\\\\", \\\\\\\"접수일시\\\\\\\": \\\\\\\"2026-10-24 03:53:51\\\\\\\", \\\\\\\"고객사아이디\\\\\\\": \\\\\\\"joeun\\\\\\\", \\\\\\\"고객사상호\\\\\\\": \\\\\\\"주식회사 조은로직스\\\\\\\", \\\\\\\"화주상호\\\\\\\": \\\\\\\"주식회사 조은로직스\\\\\\\", \\\\\\\"화주주소\\\\\\\": \\\\\\\"112\\\\\\\", \\\\\\\"화주전화번호\\\\\\\": \\\\\\\"2112\\\\\\\", \\\\\\\"해외수하인\\\\\\\": \\\\\\\"1212\\\\\\\", \\\\\\\"해외수하인주소\\\\\\\": \\\\\\\"121\\\\\\\", \\\\\\\"해외수하인전화번호\\\\\\\": \\\\\\\"121\\\\\\\", \\\\\\\"도착국가\\\\\\\": \\\\\\\"미국\\\\\\\", \\\\\\\"품목\\\\\\\": \\\\\\\"보톡스\\\\\\\", \\\\\\\"운송형태\\\\\\\": \\\\\\\"항공(Air)\\\\\\\", \\\\\\\"실제중량kg\\\\\\\": \\\\\\\"10.00\\\\\\\", \\\\\\\"가로cm\\\\\\\": \\\\\\\"25.50\\\\\\\", \\\\\\\"세로cm\\\\\\\": \\\\\\\"35.00\\\\\\\", \\\\\\\"높이cm\\\\\\\": \\\\\\\"10.00\\\\\\\", \\\\\\\"박스수량\\\\\\\": \\\\\\\"1\\\\\\\", \\\\\\\"CBM\\\\\\\": \\\\\\\"0.0089\\\\\\\", \\\\\\\"부피중량kg\\\\\\\": \\\\\\\"1.78\\\\\\\", \\\\\\\"추가요청\\\\\\\": \\\\\\\"\\\\\\\", \\\\\\\"상태\\\\\\\": \\\\\\\"B/L 등록\\\\\\\", \\\\\\\"연결 B/L 번호\\\\\\\": \\\\\\\"BW260027\\\\\\\", \\\\\\\"변경요청JSON\\\\\\\": \\\\\\\"\\\\\\\", \\\\\\\"관리자메모\\\\\\\": \\\\\\\"\\\\\\\", \\\\\\\"승인일시\\\\\\\": \\\\\\\"2026-10-24 04:13:29\\\\\\\", \\\\\\\"승인자\\\\\\\": \\\\\\\"lsb\\\\\\\", \\\\\\\"B/L등록일시\\\\\\\": \\\\\\\"2026-10-24 04:28:57\\\\\\\", \\\\\\\"박스별정보JSON\\\\\\\": \\\\\\\"\\\\\\\", \\\\\\\"바코드목록JSON\\\\\\\": \\\\\\\"\\\\\\\", \\\\\\\"수출면장번호\\\\\\\": \\\\\\\"\\\\\\\"}}\\\", \\\"관리자메모\\\": \\\"\\\", \\\"승인일시\\\": \\\"2026-10-24 04:13:29\\\", \\\"승인자\\\": \\\"lsb\\\", \\\"B/L등록일시\\\": \\\"2026-10-24 04:28:57\\\", \\\"박스별정보JSON\\\": \\\"\\\", \\\"바코드목록JSON\\\": \\\"\\\", \\\"수출면장번호\\\": \\\"\\\"}}\", \"관리자메모\": \"\", \"승인일시\": \"2026-10-24 04:13:29\", \"승인자\": \"lsb\", \"B/L등록일시\": \"2026-10-24 04:28:57\", \"박스별정보JSON\": \"[{\\\"박스순번\\\": 1, \\\"가로cm\\\": 25.5, \\\"세로cm\\\": 35.0, \\\"높이cm\\\": 10.0, \\\"바코드\\\": \\\"BW261031-6910F6F3\\\", \\\"입고상태\\\": \\\"미입고\\\"}]\", \"바코드목록JSON\": \"[\\\"BW261031-6910F6F3\\\"]\", \"수출면장번호\": \"\"}"}, {"일시": "2026-10-31 04:46:51", "접수번호": "REQ-5E48AE99B9", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 미등록 접수 삭제", "변경내용": "{\"접수번호\": \"REQ-5E48AE99B9\", \"접수일시\": \"2026-10-31 03:34:00\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"we\", \"화주전화번호\": \"ewwe\", \"해외수하인\": \"wew\", \"해외수하인주소\": \"wew\", \"해외수하인전화번호\": \"we\", \"도착국가\": \"미국\", \"품목\": \"일반화물\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"2.00\", \"가로cm\": \"26.00\", \"세로cm\": \"33.00\", \"높이cm\": \"45.00\", \"박스수량\": \"1\", \"CBM\": \"0.0386\", \"부피중량kg\": \"7.72\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\", \"승인일시\": \"\", \"승인자\": \"\", \"B/L등록일시\": \"\", \"박스별정보JSON\": \"[{\\\"박스순번\\\": 1, \\\"가로cm\\\": 26.0, \\\"세로cm\\\": 33.0, \\\"높이cm\\\": 45.0, \\\"실제중량kg\\\": \\\"\\\", \\\"바코드\\\": \\\"BW261031-AF70AD8A\\\", \\\"입고상태\\\": \\\"미입고\\\"}]\", \"바코드목록JSON\": \"[\\\"BW261031-AF70AD8A\\\"]\", \"수출면장번호\": \"\"}"}]}</t>
         </is>
       </c>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>미지급</t>
+          <t>지급완료</t>
         </is>
       </c>
     </row>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>미지급</t>
+          <t>지급완료</t>
         </is>
       </c>
     </row>
@@ -16000,7 +16000,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>미지급</t>
+          <t>지급완료</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>미지급</t>
+          <t>지급완료</t>
         </is>
       </c>
     </row>
@@ -16060,7 +16060,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>미지급</t>
+          <t>지급완료</t>
         </is>
       </c>
     </row>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>미지급</t>
+          <t>지급완료</t>
         </is>
       </c>
     </row>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>미지급</t>
+          <t>지급완료</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>미지급</t>
+          <t>지급완료</t>
         </is>
       </c>
     </row>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>미지급</t>
+          <t>지급완료</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>미지급</t>
+          <t>지급완료</t>
         </is>
       </c>
     </row>
@@ -16615,7 +16615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16759,6 +16759,21 @@
           <t>B/L등록일시</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>박스별정보JSON</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>바코드목록JSON</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>수출면장번호</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16864,7 +16879,7 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>B/L 등록</t>
+          <t>B/L 등록 후 수정 승인 대기</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -16872,7 +16887,11 @@
           <t>BW260027</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>{"요청일시": "2026-10-31 03:40:01", "요청자": "주식회사 조은로직스", "변경후": {"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록 후 수정 승인 대기", "연결 B/L 번호": "BW260027", "변경요청JSON": "{\"요청일시\": \"2026-10-31 03:39:59\", \"요청자\": \"주식회사 조은로직스\", \"변경후\": {\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"B/L 등록\", \"연결 B/L 번호\": \"BW260027\", \"변경요청JSON\": \"\", \"관리자메모\": \"\", \"승인일시\": \"2026-10-24 04:13:29\", \"승인자\": \"lsb\", \"B/L등록일시\": \"2026-10-24 04:28:57\", \"박스별정보JSON\": \"\", \"바코드목록JSON\": \"\", \"수출면장번호\": \"\"}}", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57", "박스별정보JSON": "", "바코드목록JSON": "", "수출면장번호": ""}}</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
@@ -16889,6 +16908,392 @@
           <t>2026-10-24 04:28:57</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>[{"박스순번": 1, "가로cm": 25.5, "세로cm": 35.0, "높이cm": 10.0, "바코드": "BW261031-6910F6F3", "입고상태": "미입고"}]</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>["BW261031-6910F6F3"]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-1352AC8EF3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-31 03:34:11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>we</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ewwe</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>wew</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>wew</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>we</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>일반화물</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>26.00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>33.00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.0386</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>접수</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>[{"박스순번": 1, "가로cm": 26.0, "세로cm": 33.0, "높이cm": 45.0, "실제중량kg": "", "바코드": "BW261031-30199F3C", "입고상태": "미입고"}]</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>["BW261031-30199F3C"]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-8D0365C209</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-31 03:34:11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>we</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ewwe</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>wew</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>wew</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>we</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>일반화물</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>26.00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>33.00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.0386</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>접수</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>[{"박스순번": 1, "가로cm": 26.0, "세로cm": 33.0, "높이cm": 45.0, "실제중량kg": "", "바코드": "BW261031-5EAD2C54", "입고상태": "미입고"}]</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>["BW261031-5EAD2C54"]</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-F3132C22A5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-31 03:34:29</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>we</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ewwe</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>wew</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>wew</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>we</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>일반화물</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>26.00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>33.00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.0386</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>접수</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>[{"박스순번": 1, "가로cm": 26.0, "세로cm": 33.0, "높이cm": 45.0, "실제중량kg": "", "바코드": "BW261031-EE30092E", "입고상태": "미입고"}]</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>["BW261031-EE30092E"]</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16901,7 +17306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17213,6 +17618,262 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>BW260027</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-31 03:34:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>REQ-5E48AE99B9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>신규 접수 및 박스별 바코드 발급</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>{"접수번호": "REQ-5E48AE99B9", "접수일시": "2026-10-31 03:34:00", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "we", "화주전화번호": "ewwe", "해외수하인": "wew", "해외수하인주소": "wew", "해외수하인전화번호": "we", "도착국가": "미국", "품목": "일반화물", "운송형태": "항공(Air)", "실제중량kg": "2.00", "가로cm": "26.00", "세로cm": "33.00", "높이cm": "45.00", "박스수량": "1", "CBM": "0.0386", "부피중량kg": "7.72", "박스별정보JSON": "[{\"박스순번\": 1, \"가로cm\": 26.0, \"세로cm\": 33.0, \"높이cm\": 45.0, \"실제중량kg\": \"\", \"바코드\": \"BW261031-AF70AD8A\", \"입고상태\": \"미입고\"}]", "바코드목록JSON": "[\"BW261031-AF70AD8A\"]", "수출면장번호": "", "추가요청": "", "상태": "접수", "연결 B/L 번호": "", "변경요청JSON": "", "관리자메모": ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-31 03:34:11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>REQ-1352AC8EF3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>신규 접수 및 박스별 바코드 발급</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>{"접수번호": "REQ-1352AC8EF3", "접수일시": "2026-10-31 03:34:11", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "we", "화주전화번호": "ewwe", "해외수하인": "wew", "해외수하인주소": "wew", "해외수하인전화번호": "we", "도착국가": "미국", "품목": "일반화물", "운송형태": "항공(Air)", "실제중량kg": "2.00", "가로cm": "26.00", "세로cm": "33.00", "높이cm": "45.00", "박스수량": "1", "CBM": "0.0386", "부피중량kg": "7.72", "박스별정보JSON": "[{\"박스순번\": 1, \"가로cm\": 26.0, \"세로cm\": 33.0, \"높이cm\": 45.0, \"실제중량kg\": \"\", \"바코드\": \"BW261031-30199F3C\", \"입고상태\": \"미입고\"}]", "바코드목록JSON": "[\"BW261031-30199F3C\"]", "수출면장번호": "", "추가요청": "", "상태": "접수", "연결 B/L 번호": "", "변경요청JSON": "", "관리자메모": ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-31 03:34:11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>REQ-8D0365C209</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>신규 접수 및 박스별 바코드 발급</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>{"접수번호": "REQ-8D0365C209", "접수일시": "2026-10-31 03:34:11", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "we", "화주전화번호": "ewwe", "해외수하인": "wew", "해외수하인주소": "wew", "해외수하인전화번호": "we", "도착국가": "미국", "품목": "일반화물", "운송형태": "항공(Air)", "실제중량kg": "2.00", "가로cm": "26.00", "세로cm": "33.00", "높이cm": "45.00", "박스수량": "1", "CBM": "0.0386", "부피중량kg": "7.72", "박스별정보JSON": "[{\"박스순번\": 1, \"가로cm\": 26.0, \"세로cm\": 33.0, \"높이cm\": 45.0, \"실제중량kg\": \"\", \"바코드\": \"BW261031-5EAD2C54\", \"입고상태\": \"미입고\"}]", "바코드목록JSON": "[\"BW261031-5EAD2C54\"]", "수출면장번호": "", "추가요청": "", "상태": "접수", "연결 B/L 번호": "", "변경요청JSON": "", "관리자메모": ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-31 03:34:29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>REQ-F3132C22A5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>신규 접수 및 박스별 바코드 발급</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>{"접수번호": "REQ-F3132C22A5", "접수일시": "2026-10-31 03:34:29", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "we", "화주전화번호": "ewwe", "해외수하인": "wew", "해외수하인주소": "wew", "해외수하인전화번호": "we", "도착국가": "미국", "품목": "일반화물", "운송형태": "항공(Air)", "실제중량kg": "2.00", "가로cm": "26.00", "세로cm": "33.00", "높이cm": "45.00", "박스수량": "1", "CBM": "0.0386", "부피중량kg": "7.72", "박스별정보JSON": "[{\"박스순번\": 1, \"가로cm\": 26.0, \"세로cm\": 33.0, \"높이cm\": 45.0, \"실제중량kg\": \"\", \"바코드\": \"BW261031-EE30092E\", \"입고상태\": \"미입고\"}]", "바코드목록JSON": "[\"BW261031-EE30092E\"]", "수출면장번호": "", "추가요청": "", "상태": "접수", "연결 B/L 번호": "", "변경요청JSON": "", "관리자메모": ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-31 03:39:59</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>REQ-A458BDB2B3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>B/L 등록 후 수정 승인 요청</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57", "박스별정보JSON": "", "바코드목록JSON": "", "수출면장번호": ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-31 03:40:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>REQ-A458BDB2B3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>B/L 등록 후 수정 승인 요청</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록 후 수정 승인 대기", "연결 B/L 번호": "BW260027", "변경요청JSON": "{\"요청일시\": \"2026-10-31 03:39:59\", \"요청자\": \"주식회사 조은로직스\", \"변경후\": {\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"B/L 등록\", \"연결 B/L 번호\": \"BW260027\", \"변경요청JSON\": \"\", \"관리자메모\": \"\", \"승인일시\": \"2026-10-24 04:13:29\", \"승인자\": \"lsb\", \"B/L등록일시\": \"2026-10-24 04:28:57\", \"박스별정보JSON\": \"\", \"바코드목록JSON\": \"\", \"수출면장번호\": \"\"}}", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57", "박스별정보JSON": "", "바코드목록JSON": "", "수출면장번호": ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-31 03:45:21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>REQ-A458BDB2B3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>기존 접수 건 QR·바코드 보완 발급</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록 후 수정 승인 대기", "연결 B/L 번호": "BW260027", "변경요청JSON": "{\"요청일시\": \"2026-10-31 03:40:01\", \"요청자\": \"주식회사 조은로직스\", \"변경후\": {\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"B/L 등록 후 수정 승인 대기\", \"연결 B/L 번호\": \"BW260027\", \"변경요청JSON\": \"{\\\"요청일시\\\": \\\"2026-10-31 03:39:59\\\", \\\"요청자\\\": \\\"주식회사 조은로직스\\\", \\\"변경후\\\": {\\\"접수번호\\\": \\\"REQ-A458BDB2B3\\\", \\\"접수일시\\\": \\\"2026-10-24 03:53:51\\\", \\\"고객사아이디\\\": \\\"joeun\\\", \\\"고객사상호\\\": \\\"주식회사 조은로직스\\\", \\\"화주상호\\\": \\\"주식회사 조은로직스\\\", \\\"화주주소\\\": \\\"112\\\", \\\"화주전화번호\\\": \\\"2112\\\", \\\"해외수하인\\\": \\\"1212\\\", \\\"해외수하인주소\\\": \\\"121\\\", \\\"해외수하인전화번호\\\": \\\"121\\\", \\\"도착국가\\\": \\\"미국\\\", \\\"품목\\\": \\\"보톡스\\\", \\\"운송형태\\\": \\\"항공(Air)\\\", \\\"실제중량kg\\\": \\\"10.00\\\", \\\"가로cm\\\": \\\"25.50\\\", \\\"세로cm\\\": \\\"35.00\\\", \\\"높이cm\\\": \\\"10.00\\\", \\\"박스수량\\\": \\\"1\\\", \\\"CBM\\\": \\\"0.0089\\\", \\\"부피중량kg\\\": \\\"1.78\\\", \\\"추가요청\\\": \\\"\\\", \\\"상태\\\": \\\"B/L 등록\\\", \\\"연결 B/L 번호\\\": \\\"BW260027\\\", \\\"변경요청JSON\\\": \\\"\\\", \\\"관리자메모\\\": \\\"\\\", \\\"승인일시\\\": \\\"2026-10-24 04:13:29\\\", \\\"승인자\\\": \\\"lsb\\\", \\\"B/L등록일시\\\": \\\"2026-10-24 04:28:57\\\", \\\"박스별정보JSON\\\": \\\"\\\", \\\"바코드목록JSON\\\": \\\"\\\", \\\"수출면장번호\\\": \\\"\\\"}}\", \"관리자메모\": \"\", \"승인일시\": \"2026-10-24 04:13:29\", \"승인자\": \"lsb\", \"B/L등록일시\": \"2026-10-24 04:28:57\", \"박스별정보JSON\": \"\", \"바코드목록JSON\": \"\", \"수출면장번호\": \"\"}}", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57", "박스별정보JSON": "[{\"박스순번\": 1, \"가로cm\": 25.5, \"세로cm\": 35.0, \"높이cm\": 10.0, \"바코드\": \"BW261031-6910F6F3\", \"입고상태\": \"미입고\"}]", "바코드목록JSON": "[\"BW261031-6910F6F3\"]", "수출면장번호": ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-31 04:46:51</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>REQ-5E48AE99B9</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>joeun</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lsb</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>B/L 미등록 접수 삭제</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>{"접수번호": "REQ-5E48AE99B9", "접수일시": "2026-10-31 03:34:00", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "we", "화주전화번호": "ewwe", "해외수하인": "wew", "해외수하인주소": "wew", "해외수하인전화번호": "we", "도착국가": "미국", "품목": "일반화물", "운송형태": "항공(Air)", "실제중량kg": "2.00", "가로cm": "26.00", "세로cm": "33.00", "높이cm": "45.00", "박스수량": "1", "CBM": "0.0386", "부피중량kg": "7.72", "추가요청": "", "상태": "접수", "연결 B/L 번호": "", "변경요청JSON": "", "관리자메모": "", "승인일시": "", "승인자": "", "B/L등록일시": "", "박스별정보JSON": "[{\"박스순번\": 1, \"가로cm\": 26.0, \"세로cm\": 33.0, \"높이cm\": 45.0, \"실제중량kg\": \"\", \"바코드\": \"BW261031-AF70AD8A\", \"입고상태\": \"미입고\"}]", "바코드목록JSON": "[\"BW261031-AF70AD8A\"]", "수출면장번호": ""}</t>
         </is>
       </c>
     </row>
